--- a/artfynd/A 27708-2024 artfynd.xlsx
+++ b/artfynd/A 27708-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118611275</v>
+        <v>105920045</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kammartorp (Kammartorp), Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579275</v>
+        <v>579174</v>
       </c>
       <c r="R2" t="n">
-        <v>6398015</v>
+        <v>6398184</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,21 +765,241 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118608293</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kärren, Kärren, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>579256</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6398133</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Louise Lundberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Louise Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118611275</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kammartorp, Kammartorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579275</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398015</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
